--- a/create_forecast_basic/future/bau/Intermediates/240703_pop_2050_bau.xlsx
+++ b/create_forecast_basic/future/bau/Intermediates/240703_pop_2050_bau.xlsx
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1518.880760635146</v>
+        <v>1518.880760635145</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>4596.95529565095</v>
+        <v>4596.955295650952</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>4064.435855247981</v>
+        <v>4064.435855247984</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>18734.84936780013</v>
+        <v>18734.84936780011</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>10625.40039917612</v>
+        <v>10625.40039917611</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>18616.15539330787</v>
+        <v>18616.15539330788</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>50237.98144499646</v>
+        <v>50237.98144499648</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>37138.88477115368</v>
+        <v>37138.88477115364</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>11966.53104400984</v>
+        <v>11966.53104400985</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1757.556404556162</v>
+        <v>1757.556404556163</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>8611.030039720728</v>
+        <v>8611.03003972073</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>2716.742776104742</v>
+        <v>2716.742776104744</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>15523.23023790245</v>
+        <v>15523.23023790243</v>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>3660.900832810687</v>
+        <v>3660.900832810684</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>9091.052877980699</v>
+        <v>9091.052877980683</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>8386.590834296972</v>
+        <v>8386.590834296969</v>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>45640.9662853259</v>
+        <v>45640.96628532591</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>12195.97182881198</v>
+        <v>12195.97182881199</v>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>15412.02546738571</v>
+        <v>15412.0254673857</v>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>33100.77510046069</v>
+        <v>33100.77510046071</v>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>7265.895619651596</v>
+        <v>7265.8956196516</v>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>6123.768482049434</v>
+        <v>6123.768482049433</v>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>4805.434746091984</v>
+        <v>4805.434746091983</v>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>758.9941392370163</v>
+        <v>758.994139237016</v>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>4333.429790695624</v>
+        <v>4333.429790695627</v>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>2851.52942663529</v>
+        <v>2851.529426635289</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>4839.403224105657</v>
+        <v>4839.403224105658</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>8196.023825370923</v>
+        <v>8196.023825370921</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>4059.949525693156</v>
+        <v>4059.949525693158</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>3248.535602387202</v>
+        <v>3248.535602387201</v>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>5032.342877521954</v>
+        <v>5032.342877521955</v>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>5627.669030518975</v>
+        <v>5627.669030518974</v>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>6457.959038019636</v>
+        <v>6457.959038019638</v>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>9567.949671950097</v>
+        <v>9567.949671950093</v>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>6700.329642432981</v>
+        <v>6700.329642432979</v>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>67347.11080916658</v>
+        <v>67347.11080916662</v>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>58376.01370577871</v>
+        <v>58376.01370577869</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
-        <v>61753.34437533776</v>
+        <v>61753.34437533773</v>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
-        <v>80276.26303785456</v>
+        <v>80276.26303785457</v>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
-        <v>100340.616782781</v>
+        <v>100340.6167827809</v>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>2078.456122337161</v>
+        <v>2078.456122337159</v>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>18706.51571220111</v>
+        <v>18706.5157122011</v>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
-        <v>10789.31322816424</v>
+        <v>10789.31322816425</v>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
-        <v>4055.812628624863</v>
+        <v>4055.812628624862</v>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>5365.973484845469</v>
+        <v>5365.973484845471</v>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="n">
-        <v>13657.89023430727</v>
+        <v>13657.89023430726</v>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>17643.89165186434</v>
+        <v>17643.89165186432</v>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
-        <v>6363.389502865741</v>
+        <v>6363.389502865742</v>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
-        <v>34524.42486474628</v>
+        <v>34524.42486474626</v>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>21267.41345431392</v>
+        <v>21267.41345431393</v>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>84011.00650073164</v>
+        <v>84011.00650073175</v>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>14140.89986242236</v>
+        <v>14140.89986242235</v>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>26407.46142611738</v>
+        <v>26407.46142611739</v>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
-        <v>34039.29817542878</v>
+        <v>34039.29817542875</v>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>47635.52965129723</v>
+        <v>47635.52965129724</v>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
-        <v>9741.723575339665</v>
+        <v>9741.723575339667</v>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
-        <v>7776.186947181794</v>
+        <v>7776.186947181792</v>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
-        <v>4189.780164398784</v>
+        <v>4189.780164398786</v>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
-        <v>4728.151750103202</v>
+        <v>4728.151750103203</v>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>5531.061235036696</v>
+        <v>5531.061235036695</v>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>14670.99298363003</v>
+        <v>14670.99298363001</v>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>8562.423842440459</v>
+        <v>8562.423842440456</v>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
-        <v>51694.51309391279</v>
+        <v>51694.51309391278</v>
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
-        <v>53304.62795019934</v>
+        <v>53304.62795019933</v>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
-        <v>36547.16885909747</v>
+        <v>36547.16885909746</v>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
-        <v>50546.06146141519</v>
+        <v>50546.06146141524</v>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
-        <v>37861.44872202112</v>
+        <v>37861.44872202111</v>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
